--- a/results/Int Task Remove ACC -0.4/Rando_5_permute.xlsx
+++ b/results/Int Task Remove ACC -0.4/Rando_5_permute.xlsx
@@ -440,297 +440,297 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.783316048742546</v>
+        <v>0.7912501560414447</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7823701975244626</v>
+        <v>0.8039195210247841</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8027624136970779</v>
+        <v>0.8039195210247841</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.792631722985625</v>
+        <v>0.8039195210247841</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7939028605997753</v>
+        <v>0.8039195210247841</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.793896859005752</v>
+        <v>0.8207888015056799</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7916258558273077</v>
+        <v>0.8335661951814402</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7900234302230673</v>
+        <v>0.8315244528946888</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7813367230336377</v>
+        <v>0.8344400272712432</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7819752926377246</v>
+        <v>0.8386387424499947</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7844755567078616</v>
+        <v>0.8379641632817676</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7626057480866918</v>
+        <v>0.8379641632817676</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7626057480866918</v>
+        <v>0.8355119119638177</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7619791816706517</v>
+        <v>0.837722899202028</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7634915833645417</v>
+        <v>0.8333549390718175</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7622264473444147</v>
+        <v>0.8321258126158309</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7640821402164415</v>
+        <v>0.8321438173979009</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7675282555046621</v>
+        <v>0.8311859629917706</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7690946715447623</v>
+        <v>0.8450424432729333</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7855534429944593</v>
+        <v>0.8411810176782953</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7855534429944593</v>
+        <v>0.8424521552924457</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7717329722774369</v>
+        <v>0.8421268688963788</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7756364090302383</v>
+        <v>0.8340235166460211</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7753411306042886</v>
+        <v>0.8274325660895534</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7628590153544782</v>
+        <v>0.8399218832521917</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7628590153544782</v>
+        <v>0.8399218832521917</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7580097273835931</v>
+        <v>0.8512000787409135</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7506913836314926</v>
+        <v>0.826047398188959</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.740160986758083</v>
+        <v>0.7921455938697317</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7248473194480454</v>
+        <v>0.7552705998713258</v>
       </c>
     </row>
     <row r="32">
@@ -740,197 +740,197 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6851395730706076</v>
+        <v>0.704868012944238</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6603133792335244</v>
+        <v>0.6957227839714228</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6648253776202959</v>
+        <v>0.6995854098848655</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6418968878134033</v>
+        <v>0.7027014375018005</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6451257453979777</v>
+        <v>0.656129067880429</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.637734182198792</v>
+        <v>0.6760963711961897</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6060277609733145</v>
+        <v>0.661077982312102</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6231443071279732</v>
+        <v>0.6569152766974908</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6127339421350311</v>
+        <v>0.6006143231642325</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6623155109997216</v>
+        <v>0.567594753166441</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6850399466098196</v>
+        <v>0.566016333938294</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6884260459578064</v>
+        <v>0.6020979172068102</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6874681915516762</v>
+        <v>0.5824450974178742</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6725098186078222</v>
+        <v>0.5876976925071299</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6725098186078222</v>
+        <v>0.6064706786122394</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.656073853215414</v>
+        <v>0.6064526738301692</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6473199281729227</v>
+        <v>0.6115192195047005</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.622775809254938</v>
+        <v>0.595253699382556</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.619914249224594</v>
+        <v>0.595253699382556</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6170166796301098</v>
+        <v>0.5497244068024467</v>
       </c>
     </row>
     <row r="52">
@@ -940,387 +940,387 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6173419660261765</v>
+        <v>0.5569059142108144</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6112335436291879</v>
+        <v>0.5589056453394021</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6173239612441064</v>
+        <v>0.5601707813595291</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.6131792604115653</v>
+        <v>0.5518141618413851</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.6261018926626912</v>
+        <v>0.5328995381173239</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.6226917869386108</v>
+        <v>0.5372194854953476</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.6339219696751457</v>
+        <v>0.5343807315222924</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.6177140648556256</v>
+        <v>0.5135275929286819</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.6143099607255688</v>
+        <v>0.4979906663209749</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5876160708284121</v>
+        <v>0.5073399494905847</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5534946081679294</v>
+        <v>0.5156173479676203</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5429113972671141</v>
+        <v>0.525309922315367</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.4919782694283601</v>
+        <v>0.5247505737523886</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4950738916256158</v>
+        <v>0.4846371196189708</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.4759456111543226</v>
+        <v>0.5047472608724878</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.4778073056203728</v>
+        <v>0.501939715188354</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4939155839791048</v>
+        <v>0.5019097072182371</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5102363187662643</v>
+        <v>0.4971924543158663</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4963366270081334</v>
+        <v>0.4971924543158663</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5164563708120877</v>
+        <v>0.4925112109776357</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5214809053284553</v>
+        <v>0.490570295470477</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5226908266835671</v>
+        <v>0.469586322127157</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5249378234859179</v>
+        <v>0.4487295825771325</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5149547719874399</v>
+        <v>0.4588518710569527</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5149547719874399</v>
+        <v>0.5208111274354469</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5227148330596607</v>
+        <v>0.5091872401309788</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4807072758524664</v>
+        <v>0.5121676317229856</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4951951238248879</v>
+        <v>0.547005684709859</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4997551349638464</v>
+        <v>0.5385698441506064</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5066821747856231</v>
+        <v>0.5336761443839484</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5063628899835797</v>
+        <v>0.5067025802053026</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5014475844784374</v>
+        <v>0.5675455400954493</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5014475844784374</v>
+        <v>0.5658338854799835</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4860294894323932</v>
+        <v>0.5679728535899136</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4764281393138017</v>
+        <v>0.5680148647480772</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4758135760858084</v>
+        <v>0.5718582855606449</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4925940329751582</v>
+        <v>0.5565566214386541</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4950954973640999</v>
+        <v>0.5295134387693372</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4950834941760532</v>
+        <v>0.4984551896983839</v>
       </c>
     </row>
   </sheetData>
